--- a/data.xlsx
+++ b/data.xlsx
@@ -134,7 +134,7 @@
     <t>Haier 4 Doors Refrigerator Glass/Piano Black</t>
   </si>
   <si>
-    <t>https://image.haier.com/my/refrigerators/W020240607350194166815_1200.png</t>
+    <t>https://image.haier.com/my/refrigerators/W020240119438969168883_1200.jpg</t>
   </si>
   <si>
     <t>https://image.haier.com/my/refrigerators/W020240607350194815441_1200.png</t>
@@ -438,7 +438,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,26 +460,6 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1A1AA6"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -936,162 +916,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1634,10 +1613,10 @@
       <c r="H6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="2"/>
@@ -1665,10 +1644,10 @@
       <c r="H7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K7" s="2"/>
@@ -1696,10 +1675,10 @@
       <c r="H8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="K8" s="2"/>
@@ -1727,10 +1706,10 @@
       <c r="H9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="2"/>
@@ -1758,10 +1737,10 @@
       <c r="H10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>55</v>
       </c>
       <c r="K10" s="2"/>
@@ -1789,10 +1768,10 @@
       <c r="H11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -1822,7 +1801,7 @@
       <c r="H12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>64</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -1855,7 +1834,7 @@
       <c r="H13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>69</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -2047,7 +2026,7 @@
       <c r="H19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>95</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -2278,10 +2257,10 @@
       <c r="H26" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="5" t="s">
         <v>127</v>
       </c>
       <c r="K26" s="2"/>
@@ -2327,26 +2306,27 @@
     <hyperlink ref="J2" r:id="rId2" display="https://images.samsung.com/is/image/samsung/p6pim/my/rf48a4000b4-me/gallery/my-twin-cooling-plus-rf48a4000b4-me-401525876?$2052_1641_JPG$"/>
     <hyperlink ref="I3" r:id="rId3" display="https://www.hisense.com.my/wp-content/uploads/2024/12/7-左侧45-拷贝-scaled.jpg"/>
     <hyperlink ref="J3" r:id="rId4" display="https://www.hisense.com.my/wp-content/uploads/2024/12/2-%E6%AD%A3%E9%9D%A2%E5%85%A8%E5%BC%80-%E6%8B%B7%E8%B4%9D-scaled.jpg"/>
-    <hyperlink ref="I4" r:id="rId5" display="https://image.haier.com/my/refrigerators/W020240531384827881202_1200.png"/>
-    <hyperlink ref="J4" r:id="rId6" display="https://image.haier.com/my/refrigerators/W020240607356075475173_1200.png"/>
-    <hyperlink ref="I5" r:id="rId7" display="https://www.hisense.com.my/wp-content/uploads/2022/12/1200-x-800.1.jpg"/>
-    <hyperlink ref="J5" r:id="rId8" display="https://www.hisense.com.my/wp-content/uploads/2022/12/2-3.jpg"/>
-    <hyperlink ref="I6" r:id="rId9" display="https://image.haier.com/my/refrigerators/W020240607350194166815_1200.png"/>
-    <hyperlink ref="J6" r:id="rId10" display="https://image.haier.com/my/refrigerators/W020240607350194815441_1200.png"/>
-    <hyperlink ref="I7" r:id="rId11" display="https://image.haier.com/my/refrigerators/W020240523338937740327_1200.png"/>
-    <hyperlink ref="J7" r:id="rId12" display="https://image.haier.com/my/refrigerators/W020240523338937329605_1200.jpg"/>
-    <hyperlink ref="I8" r:id="rId13" display="https://www.senghuat.com.my/image/senghuat/image/cache/data/all_product_images/product-4859/5PRJKufD1710744536-420x420.jpg"/>
-    <hyperlink ref="J8" r:id="rId14" display="https://my.sharp/sites/default/files/styles/resize_640x640/public/uploads/2024-07/Open%2001.jpg?itok=Ehv8S7JG"/>
-    <hyperlink ref="I9" r:id="rId15" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs780wi-pgy(22)---623l-side-by-side-dual-inverter-refrigerator/GR-RS780WI-PGY(22)_04.png/jcr:content/renditions/cq5dam.compression.png"/>
-    <hyperlink ref="J9" r:id="rId16" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs780wi-pgy(22)---623l-side-by-side-dual-inverter-refrigerator/GR-RS780WI-PGY(22)_06.png/jcr:content/renditions/cq5dam.compression.png"/>
-    <hyperlink ref="I10" r:id="rId17" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs696wi-pmy(06)---620l-side-by-side-refrigerator/GR-RS696WI-PMY-06-01.png/jcr:content/renditions/cq5dam.compression.png"/>
-    <hyperlink ref="J10" r:id="rId18" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs696wi-pmy(06)---620l-side-by-side-refrigerator/GR-RS696WI-PMY-06-02.png/jcr:content/renditions/cq5dam.compression.png"/>
-    <hyperlink ref="I11" r:id="rId19" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/multi-door-refrigerator/gr-rf611wi-pgy(22)---511l-multi-door-iot-refrigerator/GR-RF611WI-PGY-22-01.png/jcr:content/renditions/GR-RF611WI-PGY-22-01.webp"/>
-    <hyperlink ref="J11" r:id="rId20" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/multi-door-refrigerator/gr-rf611wi-pgy(22)---511l-multi-door-iot-refrigerator/GR-RF611WI-PGY-22-03.png/jcr:content/renditions/GR-RF611WI-PGY-22-03.webp"/>
-    <hyperlink ref="I12" r:id="rId21" display="https://images.samsung.com/is/image/samsung/p6pim/my/rs70f65qnfme/gallery/my-rs90f-basic-rs70f65qnfme-545893209?$2052_1641_JPG$"/>
-    <hyperlink ref="I13" r:id="rId22" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/midea-aem/my/refrigerators/side-by-side-refrigerator/mdrs712fie61w/3-530%E4%BA%91%E9%95%9C%E7%99%BD-%E5%8F%B3%E4%BE%A7.png/jcr:content/renditions/cq5dam.compression.png"/>
-    <hyperlink ref="I19" r:id="rId23" display="https://www.lg.com/content/dam/channel/wcms/my/image-update/refrigerators/gc-l257kqkw/gallery/gallery-lg-com/2010x1334/2010-VS6-C_L_Di_GC-L257KQKW_NPlumb_EE_Front.jpg/_jcr_content/renditions/thum-1600x1062.jpeg"/>
+    <hyperlink ref="I5" r:id="rId5" display="https://www.hisense.com.my/wp-content/uploads/2022/12/1200-x-800.1.jpg"/>
+    <hyperlink ref="J5" r:id="rId6" display="https://www.hisense.com.my/wp-content/uploads/2022/12/2-3.jpg"/>
+    <hyperlink ref="I8" r:id="rId7" display="https://www.senghuat.com.my/image/senghuat/image/cache/data/all_product_images/product-4859/5PRJKufD1710744536-420x420.jpg"/>
+    <hyperlink ref="J8" r:id="rId8" display="https://my.sharp/sites/default/files/styles/resize_640x640/public/uploads/2024-07/Open%2001.jpg?itok=Ehv8S7JG"/>
+    <hyperlink ref="I9" r:id="rId9" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs780wi-pgy(22)---623l-side-by-side-dual-inverter-refrigerator/GR-RS780WI-PGY(22)_04.png/jcr:content/renditions/cq5dam.compression.png"/>
+    <hyperlink ref="J9" r:id="rId10" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs780wi-pgy(22)---623l-side-by-side-dual-inverter-refrigerator/GR-RS780WI-PGY(22)_06.png/jcr:content/renditions/cq5dam.compression.png"/>
+    <hyperlink ref="I10" r:id="rId11" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs696wi-pmy(06)---620l-side-by-side-refrigerator/GR-RS696WI-PMY-06-01.png/jcr:content/renditions/cq5dam.compression.png"/>
+    <hyperlink ref="J10" r:id="rId12" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/side-by-side-refrigerator/gr-rs696wi-pmy(06)---620l-side-by-side-refrigerator/GR-RS696WI-PMY-06-02.png/jcr:content/renditions/cq5dam.compression.png"/>
+    <hyperlink ref="I11" r:id="rId13" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/multi-door-refrigerator/gr-rf611wi-pgy(22)---511l-multi-door-iot-refrigerator/GR-RF611WI-PGY-22-01.png/jcr:content/renditions/GR-RF611WI-PGY-22-01.webp"/>
+    <hyperlink ref="J11" r:id="rId14" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/toshiba-aem/my/refrigerator/multi-door-refrigerator/gr-rf611wi-pgy(22)---511l-multi-door-iot-refrigerator/GR-RF611WI-PGY-22-03.png/jcr:content/renditions/GR-RF611WI-PGY-22-03.webp"/>
+    <hyperlink ref="I12" r:id="rId15" display="https://images.samsung.com/is/image/samsung/p6pim/my/rs70f65qnfme/gallery/my-rs90f-basic-rs70f65qnfme-545893209?$2052_1641_JPG$"/>
+    <hyperlink ref="I13" r:id="rId16" display="https://d1pjg4o0tbonat.cloudfront.net/content/dam/midea-aem/my/refrigerators/side-by-side-refrigerator/mdrs712fie61w/3-530%E4%BA%91%E9%95%9C%E7%99%BD-%E5%8F%B3%E4%BE%A7.png/jcr:content/renditions/cq5dam.compression.png"/>
+    <hyperlink ref="I19" r:id="rId17" display="https://www.lg.com/content/dam/channel/wcms/my/image-update/refrigerators/gc-l257kqkw/gallery/gallery-lg-com/2010x1334/2010-VS6-C_L_Di_GC-L257KQKW_NPlumb_EE_Front.jpg/_jcr_content/renditions/thum-1600x1062.jpeg"/>
+    <hyperlink ref="I4" r:id="rId18" display="https://image.haier.com/my/refrigerators/W020240531384827881202_1200.png"/>
+    <hyperlink ref="J4" r:id="rId19" display="https://image.haier.com/my/refrigerators/W020240607356075475173_1200.png"/>
+    <hyperlink ref="I6" r:id="rId20" display="https://image.haier.com/my/refrigerators/W020240119438969168883_1200.jpg"/>
+    <hyperlink ref="J6" r:id="rId21" display="https://image.haier.com/my/refrigerators/W020240607350194815441_1200.png"/>
+    <hyperlink ref="I7" r:id="rId22" display="https://image.haier.com/my/refrigerators/W020240523338937740327_1200.png"/>
+    <hyperlink ref="J7" r:id="rId23" display="https://image.haier.com/my/refrigerators/W020240523338937329605_1200.jpg"/>
     <hyperlink ref="I26" r:id="rId24" display="https://image.haier.com/my/refrigerators/W020240611369085807355_1200.jpg"/>
+    <hyperlink ref="J26" r:id="rId25" display="https://image.haier.com/my/refrigerators/W020240611369086512717_1200.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
